--- a/data/trans_camb/P38B-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P38B-Habitat-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,96; 5,13</t>
+          <t>-3,38; 4,4</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 8,86</t>
+          <t>-0,98; 8,67</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,31; 5,01</t>
+          <t>-1,99; 5,08</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,96; 9,68</t>
+          <t>3,12; 9,41</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,79; 3,85</t>
+          <t>-1,74; 3,51</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,17; 8,03</t>
+          <t>2,2; 8,06</t>
         </is>
       </c>
     </row>
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,47; 6,3</t>
+          <t>-3,97; 5,44</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 11,07</t>
+          <t>-1,18; 10,72</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,65; 5,92</t>
+          <t>-2,27; 6,08</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,33; 11,52</t>
+          <t>3,47; 11,19</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 4,59</t>
+          <t>-2,02; 4,2</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,57; 9,62</t>
+          <t>2,44; 9,67</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,62; 4,62</t>
+          <t>-2,67; 4,34</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-47,74; -2,2</t>
+          <t>-52,07; -2,11</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,54; 7,15</t>
+          <t>1,68; 7,39</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,51; 1,59</t>
+          <t>-4,49; 1,46</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,37; 5,05</t>
+          <t>0,38; 4,82</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-35,11; -1,49</t>
+          <t>-35,87; -1,94</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,14; 5,83</t>
+          <t>-3,2; 5,39</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-59,04; -2,63</t>
+          <t>-64,2; -2,6</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,76; 8,53</t>
+          <t>1,9; 8,72</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-5,13; 1,86</t>
+          <t>-5,13; 1,73</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,42; 6,12</t>
+          <t>0,46; 5,84</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-41,74; -1,85</t>
+          <t>-42,19; -2,3</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-6,15; 2,2</t>
+          <t>-6,34; 2,18</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-8,21; 1,71</t>
+          <t>-8,51; 1,62</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-5,26; 0,84</t>
+          <t>-5,0; 1,11</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,17; 5,08</t>
+          <t>-4,84; 5,91</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-4,56; 0,39</t>
+          <t>-4,68; 0,67</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-5,06; 4,0</t>
+          <t>-4,85; 4,5</t>
         </is>
       </c>
     </row>
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-7,22; 2,71</t>
+          <t>-7,41; 2,69</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-9,75; 2,08</t>
+          <t>-10,08; 1,98</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-5,73; 0,95</t>
+          <t>-5,48; 1,26</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-5,71; 5,76</t>
+          <t>-5,39; 6,61</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-5,21; 0,44</t>
+          <t>-5,34; 0,78</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-5,77; 4,75</t>
+          <t>-5,6; 5,29</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,08; 2,89</t>
+          <t>-4,05; 3,57</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-5,27; 2,97</t>
+          <t>-5,38; 3,2</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-8,42; -2,11</t>
+          <t>-8,01; -1,88</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-22,49; 0,11</t>
+          <t>-22,63; 0,19</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-5,09; -0,47</t>
+          <t>-5,71; -0,89</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-14,66; 0,08</t>
+          <t>-14,14; -0,07</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-4,87; 3,61</t>
+          <t>-4,88; 4,55</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-6,35; 3,76</t>
+          <t>-6,37; 4,04</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-9,4; -2,45</t>
+          <t>-8,89; -2,16</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-25,29; 0,13</t>
+          <t>-25,08; 0,22</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-6,0; -0,62</t>
+          <t>-6,62; -1,05</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-17,27; 0,09</t>
+          <t>-16,57; -0,09</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,18; 1,63</t>
+          <t>-2,1; 1,58</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-23,96; -0,34</t>
+          <t>-25,67; -0,37</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,93; 1,21</t>
+          <t>-1,85; 1,27</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-6,32; 1,4</t>
+          <t>-6,68; 1,39</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 0,92</t>
+          <t>-1,63; 0,96</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-13,92; -0,04</t>
+          <t>-14,53; -0,01</t>
         </is>
       </c>
     </row>
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-2,64; 2,01</t>
+          <t>-2,53; 1,95</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-29,39; -0,44</t>
+          <t>-31,08; -0,46</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-2,16; 1,38</t>
+          <t>-2,09; 1,47</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-7,13; 1,61</t>
+          <t>-7,63; 1,58</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 1,1</t>
+          <t>-1,9; 1,13</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-16,25; -0,05</t>
+          <t>-17,05; -0,02</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P38B-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P38B-Habitat-trans_camb.xlsx
@@ -598,7 +598,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>4,25</t>
+          <t>3,76</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6,3</t>
+          <t>5,35</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,37</t>
+          <t>4,64</t>
         </is>
       </c>
     </row>
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,38; 4,4</t>
+          <t>-3,46; 4,63</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 8,67</t>
+          <t>-1,11; 8,05</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,99; 5,08</t>
+          <t>-1,95; 5,38</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,12; 9,41</t>
+          <t>2,41; 9,28</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 3,51</t>
+          <t>-1,58; 3,95</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,2; 8,06</t>
+          <t>1,94; 7,39</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>5,48%</t>
         </is>
       </c>
     </row>
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,97; 5,44</t>
+          <t>-4,08; 5,71</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 10,72</t>
+          <t>-1,09; 9,91</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,27; 6,08</t>
+          <t>-2,22; 6,42</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,47; 11,19</t>
+          <t>2,66; 11,12</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-2,02; 4,2</t>
+          <t>-1,84; 4,76</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,44; 9,67</t>
+          <t>2,26; 8,87</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>-19,41</t>
+          <t>-4,13</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-1,66</t>
+          <t>-2,06</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-11,8</t>
+          <t>-3,08</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,67; 4,34</t>
+          <t>-2,96; 4,42</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-52,07; -2,11</t>
+          <t>-8,31; -0,42</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,68; 7,39</t>
+          <t>1,5; 7,1</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,49; 1,46</t>
+          <t>-5,03; 1,34</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,38; 4,82</t>
+          <t>0,28; 4,79</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-35,87; -1,94</t>
+          <t>-5,5; -0,33</t>
         </is>
       </c>
     </row>
@@ -830,7 +830,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>-23,86%</t>
+          <t>-5,08%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -840,7 +840,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-1,92%</t>
+          <t>-2,39%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-14,06%</t>
+          <t>-3,67%</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,2; 5,39</t>
+          <t>-3,53; 5,53</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-64,2; -2,6</t>
+          <t>-9,98; -0,52</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,9; 8,72</t>
+          <t>1,69; 8,34</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-5,13; 1,73</t>
+          <t>-5,74; 1,6</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,46; 5,84</t>
+          <t>0,33; 5,82</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-42,19; -2,3</t>
+          <t>-6,48; -0,41</t>
         </is>
       </c>
     </row>
@@ -910,7 +910,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>-3,43</t>
+          <t>-4,66</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-0,54</t>
+          <t>-4,06</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-1,34</t>
+          <t>-4,39</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-6,34; 2,18</t>
+          <t>-5,83; 2,08</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-8,51; 1,62</t>
+          <t>-9,33; 0,25</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-5,0; 1,11</t>
+          <t>-5,08; 1,02</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,84; 5,91</t>
+          <t>-7,76; -0,68</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-4,68; 0,67</t>
+          <t>-4,4; 0,35</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-4,85; 4,5</t>
+          <t>-7,55; -1,66</t>
         </is>
       </c>
     </row>
@@ -986,7 +986,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>-4,12%</t>
+          <t>-5,6%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-0,6%</t>
+          <t>-4,5%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-1,55%</t>
+          <t>-5,06%</t>
         </is>
       </c>
     </row>
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-7,41; 2,69</t>
+          <t>-6,84; 2,58</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-10,08; 1,98</t>
+          <t>-11,07; 0,28</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-5,48; 1,26</t>
+          <t>-5,58; 1,17</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-5,39; 6,61</t>
+          <t>-8,47; -0,77</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-5,34; 0,78</t>
+          <t>-4,99; 0,4</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-5,6; 5,29</t>
+          <t>-8,64; -1,94</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>-0,88</t>
+          <t>-2,26</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-6,45</t>
+          <t>-2,22</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-3,8</t>
+          <t>-2,22</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,05; 3,57</t>
+          <t>-4,03; 3,32</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-5,38; 3,2</t>
+          <t>-6,18; 1,79</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-8,01; -1,88</t>
+          <t>-8,04; -1,95</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-22,63; 0,19</t>
+          <t>-5,03; 1,04</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-5,71; -0,89</t>
+          <t>-5,21; -0,54</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-14,14; -0,07</t>
+          <t>-4,92; 0,19</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>-1,08%</t>
+          <t>-2,77%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-7,31%</t>
+          <t>-2,52%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-4,47%</t>
+          <t>-2,61%</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-4,88; 4,55</t>
+          <t>-4,87; 4,18</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-6,37; 4,04</t>
+          <t>-7,47; 2,23</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-8,89; -2,16</t>
+          <t>-8,96; -2,21</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-25,08; 0,22</t>
+          <t>-5,62; 1,21</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-6,62; -1,05</t>
+          <t>-6,07; -0,64</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-16,57; -0,09</t>
+          <t>-5,69; 0,22</t>
         </is>
       </c>
     </row>
@@ -1222,7 +1222,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>-6,91</t>
+          <t>-2,19</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>-1,19</t>
+          <t>-1,09</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-3,95</t>
+          <t>-1,6</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 1,58</t>
+          <t>-2,05; 1,46</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-25,67; -0,37</t>
+          <t>-4,49; -0,09</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 1,27</t>
+          <t>-2,08; 1,05</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-6,68; 1,39</t>
+          <t>-2,64; 0,73</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-1,63; 0,96</t>
+          <t>-1,55; 0,92</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-14,53; -0,01</t>
+          <t>-3,08; -0,25</t>
         </is>
       </c>
     </row>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>-8,42%</t>
+          <t>-2,66%</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>-1,36%</t>
+          <t>-1,24%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-4,64%</t>
+          <t>-1,88%</t>
         </is>
       </c>
     </row>
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-2,53; 1,95</t>
+          <t>-2,47; 1,79</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-31,08; -0,46</t>
+          <t>-5,42; -0,11</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-2,09; 1,47</t>
+          <t>-2,35; 1,21</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-7,63; 1,58</t>
+          <t>-2,99; 0,83</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-1,9; 1,13</t>
+          <t>-1,81; 1,08</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-17,05; -0,02</t>
+          <t>-3,59; -0,29</t>
         </is>
       </c>
     </row>
